--- a/exports/LTM_full_report.xlsx
+++ b/exports/LTM_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:U71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,25 +557,25 @@
         <v>3.45</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44579.55208333334</v>
+        <v>44580.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>6867</v>
+        <v>6649.5</v>
       </c>
       <c r="I2" t="n">
         <v>6857.255000000001</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.32</v>
+        <v>-6.38</v>
       </c>
       <c r="L2" t="n">
-        <v>3.56</v>
+        <v>7.78</v>
       </c>
       <c r="M2" t="n">
-        <v>0.77</v>
+        <v>2.43</v>
       </c>
       <c r="N2" t="n">
         <v>3.47</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>6</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44593.55208333334</v>
+        <v>44594.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>6313.95</v>
+        <v>6400.25</v>
       </c>
       <c r="I3" t="n">
         <v>6335.630843049648</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K3" t="n">
-        <v>5.05</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
         <v>4.52</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44606.38541666666</v>
+        <v>44606.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>5964</v>
+        <v>5850</v>
       </c>
       <c r="I4" t="n">
         <v>5919.752212240955</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.82</v>
+        <v>-8.6</v>
       </c>
       <c r="L4" t="n">
         <v>11.25</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>9.380000000000001</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44623.55208333334</v>
+        <v>44624.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>6021</v>
+        <v>6215.2</v>
       </c>
       <c r="I5" t="n">
         <v>6071.981541731545</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>17</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.92</v>
+        <v>-6.24</v>
       </c>
       <c r="L5" t="n">
-        <v>5.3</v>
+        <v>6.63</v>
       </c>
       <c r="M5" t="n">
         <v>2.27</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>9.550000000000001</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44641.38541666666</v>
+        <v>44641.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>6011.25</v>
+        <v>5998</v>
       </c>
       <c r="I6" t="n">
         <v>6010.258647325442</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.28</v>
+        <v>-3.49</v>
       </c>
       <c r="L6" t="n">
         <v>4.87</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,25 +902,25 @@
         <v>6.48</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44655.55208333334</v>
+        <v>44656.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>6300</v>
+        <v>6396</v>
       </c>
       <c r="I7" t="n">
         <v>6361.818942822896</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.04</v>
+        <v>-6.64</v>
       </c>
       <c r="L7" t="n">
-        <v>5.67</v>
+        <v>7.19</v>
       </c>
       <c r="M7" t="n">
-        <v>0.89</v>
+        <v>1.19</v>
       </c>
       <c r="N7" t="n">
         <v>4.04</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>5.84</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44662.55208333334</v>
+        <v>44663.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>6063</v>
+        <v>5881.5</v>
       </c>
       <c r="I8" t="n">
         <v>6022.461143760091</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.21</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>6.5</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0.76</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>1.54</v>
+        <v>2.89</v>
       </c>
       <c r="O8" t="n">
         <v>0.95</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>6.97</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44708.55208333334</v>
+        <v>44711.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>4007</v>
+        <v>4193.5</v>
       </c>
       <c r="I9" t="n">
         <v>4146.045776429084</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K9" t="n">
-        <v>31.87</v>
+        <v>28.7</v>
       </c>
       <c r="L9" t="n">
         <v>3.37</v>
@@ -954,7 +1061,7 @@
         <v>2.18</v>
       </c>
       <c r="N9" t="n">
-        <v>4.59</v>
+        <v>4.82</v>
       </c>
       <c r="O9" t="n">
         <v>-2.89</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>9.65</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44727.55208333334</v>
+        <v>44728.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>4190</v>
+        <v>4078.2</v>
       </c>
       <c r="I10" t="n">
         <v>4095.966155594863</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.08</v>
+        <v>-2.75</v>
       </c>
       <c r="L10" t="n">
         <v>4.14</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>12</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44757.55208333334</v>
+        <v>44760.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>3972</v>
+        <v>4169.2</v>
       </c>
       <c r="I11" t="n">
         <v>4144.457702953429</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K11" t="n">
-        <v>2.6</v>
+        <v>-2.23</v>
       </c>
       <c r="L11" t="n">
         <v>7.4</v>
@@ -1068,7 +1199,7 @@
         <v>4.53</v>
       </c>
       <c r="N11" t="n">
-        <v>3.77</v>
+        <v>6.27</v>
       </c>
       <c r="O11" t="n">
         <v>-3.25</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>9.51</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44795.38541666666</v>
+        <v>44795.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>4752.65</v>
+        <v>4712</v>
       </c>
       <c r="I12" t="n">
         <v>4745.984559880072</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K12" t="n">
-        <v>13.99</v>
+        <v>13.02</v>
       </c>
       <c r="L12" t="n">
         <v>4.04</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>5.7</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44813.55208333334</v>
+        <v>44816.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>4670.5</v>
+        <v>4804.8</v>
       </c>
       <c r="I13" t="n">
         <v>4697.643103104755</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>18</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>0.88</v>
+        <v>-1.97</v>
       </c>
       <c r="L13" t="n">
-        <v>1.17</v>
+        <v>2.67</v>
       </c>
       <c r="M13" t="n">
         <v>1.55</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>6.08</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44818.55208333334</v>
+        <v>44819.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>4619.95</v>
+        <v>4570</v>
       </c>
       <c r="I14" t="n">
         <v>4570.156236283615</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.85</v>
+        <v>-4.89</v>
       </c>
       <c r="L14" t="n">
-        <v>5.38</v>
+        <v>5.64</v>
       </c>
       <c r="M14" t="n">
         <v>3.53</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>6.65</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44838.55208333334</v>
+        <v>44840.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>4583.95</v>
+        <v>4648</v>
       </c>
       <c r="I15" t="n">
         <v>4622.600982526177</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.31</v>
+        <v>-1.71</v>
       </c>
       <c r="L15" t="n">
-        <v>1.97</v>
+        <v>2.38</v>
       </c>
       <c r="M15" t="n">
         <v>1.93</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>6.52</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44861.55208333334</v>
+        <v>44862.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>4675</v>
+        <v>4575.75</v>
       </c>
       <c r="I16" t="n">
         <v>4585.94638659445</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K16" t="n">
-        <v>0.58</v>
+        <v>-1.55</v>
       </c>
       <c r="L16" t="n">
         <v>2.17</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>6.61</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44866.38541666666</v>
+        <v>44866.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>4781.35</v>
+        <v>4843.1</v>
       </c>
       <c r="I17" t="n">
         <v>4808.797408255381</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>-4.49</v>
+        <v>-5.84</v>
       </c>
       <c r="L17" t="n">
-        <v>4.68</v>
+        <v>6.09</v>
       </c>
       <c r="M17" t="n">
         <v>1.09</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>5.56</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44882.55208333334</v>
+        <v>44883.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>4930.95</v>
+        <v>4898.45</v>
       </c>
       <c r="I18" t="n">
         <v>4918.467242831588</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>16</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>1.81</v>
+        <v>1.14</v>
       </c>
       <c r="L18" t="n">
         <v>1.91</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>7.49</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44896.38541666666</v>
+        <v>44896.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>5007.2</v>
+        <v>5023</v>
       </c>
       <c r="I19" t="n">
         <v>5011.69741417984</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.22</v>
+        <v>-2.54</v>
       </c>
       <c r="L19" t="n">
         <v>3.6</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>5.8</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44901.38541666666</v>
+        <v>44901.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>4832.55</v>
+        <v>4800.05</v>
       </c>
       <c r="I20" t="n">
         <v>4816.151895751648</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>4.833333333333333</v>
+        <v>5</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.79</v>
+        <v>-4.44</v>
       </c>
       <c r="L20" t="n">
-        <v>4.03</v>
+        <v>4.44</v>
       </c>
       <c r="M20" t="n">
         <v>0.45</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>5.93</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44949.55208333334</v>
+        <v>44950.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>4361.15</v>
+        <v>4537</v>
       </c>
       <c r="I21" t="n">
         <v>4382.896811626792</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>48</v>
+        <v>48.83333333333334</v>
       </c>
       <c r="K21" t="n">
-        <v>9.140000000000001</v>
+        <v>5.48</v>
       </c>
       <c r="L21" t="n">
         <v>0.83</v>
@@ -1638,7 +1889,7 @@
         <v>0.76</v>
       </c>
       <c r="N21" t="n">
-        <v>2.85</v>
+        <v>3.23</v>
       </c>
       <c r="O21" t="n">
         <v>-3.48</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>7.51</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44994.55208333334</v>
+        <v>44995.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>4731</v>
+        <v>4621.05</v>
       </c>
       <c r="I22" t="n">
         <v>4685.681491839892</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K22" t="n">
-        <v>4.28</v>
+        <v>1.85</v>
       </c>
       <c r="L22" t="n">
         <v>4.54</v>
@@ -1695,7 +1958,7 @@
         <v>1.62</v>
       </c>
       <c r="N22" t="n">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="O22" t="n">
         <v>3.23</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>5.32</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45019.55208333334</v>
+        <v>45021.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>4747</v>
+        <v>4775.9</v>
       </c>
       <c r="I23" t="n">
         <v>4773.670605701613</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.73</v>
+        <v>-3.35</v>
       </c>
       <c r="L23" t="n">
         <v>3.76</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>5.32</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45029.55208333334</v>
+        <v>45033.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>4635.8</v>
+        <v>4295.7</v>
       </c>
       <c r="I24" t="n">
         <v>4628.904425123477</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.93</v>
+        <v>-10.05</v>
       </c>
       <c r="L24" t="n">
-        <v>3.35</v>
+        <v>12.44</v>
       </c>
       <c r="M24" t="n">
-        <v>0.83</v>
+        <v>3.32</v>
       </c>
       <c r="N24" t="n">
-        <v>4.02</v>
+        <v>6.75</v>
       </c>
       <c r="O24" t="n">
         <v>1.71</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>8.49</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45043.55208333334</v>
+        <v>45044.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>4322</v>
+        <v>4417.3</v>
       </c>
       <c r="I25" t="n">
         <v>4358.023896187636</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.61</v>
+        <v>-2.83</v>
       </c>
       <c r="L25" t="n">
         <v>4.34</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,25 +2213,25 @@
         <v>6.41</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45082.55208333334</v>
+        <v>45083.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>4935</v>
+        <v>4825.5</v>
       </c>
       <c r="I26" t="n">
         <v>4834.538188204557</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K26" t="n">
-        <v>11.72</v>
+        <v>9.24</v>
       </c>
       <c r="L26" t="n">
         <v>2.53</v>
       </c>
       <c r="M26" t="n">
-        <v>0.59</v>
+        <v>0.91</v>
       </c>
       <c r="N26" t="n">
         <v>2.15</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>4.23</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45093.38541666666</v>
+        <v>45093.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>4960</v>
+        <v>5008</v>
       </c>
       <c r="I27" t="n">
         <v>5000.226951712923</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.79</v>
+        <v>-3.78</v>
       </c>
       <c r="L27" t="n">
         <v>5.54</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>4.52</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45114.55208333334</v>
+        <v>45117.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>5115.7</v>
+        <v>5007.7</v>
       </c>
       <c r="I28" t="n">
         <v>5045.910946186244</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>21</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="K28" t="n">
-        <v>2.15</v>
+        <v>-0.01</v>
       </c>
       <c r="L28" t="n">
         <v>1.94</v>
@@ -2037,7 +2372,7 @@
         <v>0.44</v>
       </c>
       <c r="N28" t="n">
-        <v>1.43</v>
+        <v>2.38</v>
       </c>
       <c r="O28" t="n">
         <v>0.66</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>5.95</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45121.55208333334</v>
+        <v>45124.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>5099</v>
+        <v>5143.1</v>
       </c>
       <c r="I29" t="n">
         <v>5118.980379190303</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.82</v>
+        <v>-2.7</v>
       </c>
       <c r="L29" t="n">
-        <v>2.13</v>
+        <v>5.76</v>
       </c>
       <c r="M29" t="n">
         <v>1.03</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>5.59</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45134.55208333334</v>
+        <v>45135.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>4870</v>
+        <v>4827.75</v>
       </c>
       <c r="I30" t="n">
         <v>4855.375514391919</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K30" t="n">
-        <v>-5.31</v>
+        <v>-6.13</v>
       </c>
       <c r="L30" t="n">
-        <v>5.94</v>
+        <v>6.42</v>
       </c>
       <c r="M30" t="n">
         <v>1.75</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>4.62</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45142.55208333334</v>
+        <v>45145.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>4928.9</v>
+        <v>5057</v>
       </c>
       <c r="I31" t="n">
         <v>5021.620141435377</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.1</v>
+        <v>-4.75</v>
       </c>
       <c r="L31" t="n">
-        <v>3.54</v>
+        <v>4.77</v>
       </c>
       <c r="M31" t="n">
         <v>0.59</v>
       </c>
       <c r="N31" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="O31" t="n">
         <v>-0.61</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>5.43</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45196.55208333334</v>
+        <v>45197.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>5433.25</v>
+        <v>5277.6</v>
       </c>
       <c r="I32" t="n">
         <v>5355.843734681987</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>51.16666666666666</v>
+        <v>52</v>
       </c>
       <c r="K32" t="n">
-        <v>7.44</v>
+        <v>4.36</v>
       </c>
       <c r="L32" t="n">
         <v>2.49</v>
@@ -2265,7 +2648,7 @@
         <v>0.7</v>
       </c>
       <c r="N32" t="n">
-        <v>1.95</v>
+        <v>2.96</v>
       </c>
       <c r="O32" t="n">
         <v>2.25</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>5.77</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45217.55208333334</v>
+        <v>45218.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>5172</v>
+        <v>5448.3</v>
       </c>
       <c r="I33" t="n">
         <v>5291.741279526655</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K33" t="n">
-        <v>2</v>
+        <v>-3.23</v>
       </c>
       <c r="L33" t="n">
         <v>3.49</v>
@@ -2322,7 +2717,7 @@
         <v>0.61</v>
       </c>
       <c r="N33" t="n">
-        <v>1.39</v>
+        <v>5.67</v>
       </c>
       <c r="O33" t="n">
         <v>-2.96</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>7.31</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45222.55208333334</v>
+        <v>45224.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>5204</v>
+        <v>5185.6</v>
       </c>
       <c r="I34" t="n">
         <v>5192.179231325082</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K34" t="n">
-        <v>-4.48</v>
+        <v>-4.82</v>
       </c>
       <c r="L34" t="n">
         <v>4.83</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>6.68</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45239.38541666666</v>
+        <v>45239.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>5240</v>
+        <v>5265</v>
       </c>
       <c r="I35" t="n">
         <v>5248.024387197866</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K35" t="n">
-        <v>-1.05</v>
+        <v>-1.53</v>
       </c>
       <c r="L35" t="n">
         <v>2.11</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>3.62</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45293.55208333334</v>
+        <v>45294.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>6148.5</v>
+        <v>5975.1</v>
       </c>
       <c r="I36" t="n">
         <v>6020.452637620825</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>54</v>
+        <v>54.83333333333334</v>
       </c>
       <c r="K36" t="n">
-        <v>16.78</v>
+        <v>13.49</v>
       </c>
       <c r="L36" t="n">
         <v>1.57</v>
       </c>
       <c r="M36" t="n">
-        <v>0.54</v>
+        <v>0.63</v>
       </c>
       <c r="N36" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="O36" t="n">
         <v>0.67</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>5.93</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45302.55208333334</v>
+        <v>45303.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>5969.6</v>
+        <v>6211</v>
       </c>
       <c r="I37" t="n">
         <v>6120.660830038362</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K37" t="n">
-        <v>0.09</v>
+        <v>-3.95</v>
       </c>
       <c r="L37" t="n">
-        <v>2.31</v>
+        <v>4.27</v>
       </c>
       <c r="M37" t="n">
         <v>1.2</v>
       </c>
       <c r="N37" t="n">
-        <v>1.37</v>
+        <v>4.46</v>
       </c>
       <c r="O37" t="n">
         <v>-3.1</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>6.14</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45308.55208333334</v>
+        <v>45309.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>6280</v>
+        <v>5618.85</v>
       </c>
       <c r="I38" t="n">
         <v>6035.351539495417</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K38" t="n">
-        <v>1.11</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>3.16</v>
+        <v>12.87</v>
       </c>
       <c r="M38" t="n">
-        <v>0.82</v>
+        <v>9.24</v>
       </c>
       <c r="N38" t="n">
-        <v>0.9399999999999999</v>
+        <v>10.8</v>
       </c>
       <c r="O38" t="n">
         <v>4.46</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>8.92</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45428.38541666666</v>
+        <v>45428.55208333334</v>
       </c>
       <c r="H39" t="n">
-        <v>4710.65</v>
+        <v>4767.1</v>
       </c>
       <c r="I39" t="n">
         <v>4751.250977292417</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>119</v>
+        <v>119.1666666666667</v>
       </c>
       <c r="K39" t="n">
-        <v>16.16</v>
+        <v>15.16</v>
       </c>
       <c r="L39" t="n">
         <v>3.05</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>156</v>
+        <v>157</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>5</v>
+      </c>
+      <c r="U39" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>4.31</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45442.55208333334</v>
+        <v>45443.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>4798.85</v>
+        <v>4705.25</v>
       </c>
       <c r="I40" t="n">
         <v>4738.795397859117</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K40" t="n">
-        <v>0.67</v>
+        <v>-1.3</v>
       </c>
       <c r="L40" t="n">
-        <v>1.43</v>
+        <v>1.79</v>
       </c>
       <c r="M40" t="n">
         <v>0.64</v>
       </c>
       <c r="N40" t="n">
-        <v>1.68</v>
+        <v>2.16</v>
       </c>
       <c r="O40" t="n">
         <v>2.54</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>4.28</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45449.55208333334</v>
+        <v>45450.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>4818</v>
+        <v>4952.5</v>
       </c>
       <c r="I41" t="n">
         <v>4822.95411011209</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K41" t="n">
-        <v>-2.4</v>
+        <v>-5.25</v>
       </c>
       <c r="L41" t="n">
-        <v>2.55</v>
+        <v>6.43</v>
       </c>
       <c r="M41" t="n">
         <v>2.76</v>
       </c>
       <c r="N41" t="n">
-        <v>2.93</v>
+        <v>3.15</v>
       </c>
       <c r="O41" t="n">
         <v>-2.16</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>6.37</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45506.38541666666</v>
+        <v>45506.55208333334</v>
       </c>
       <c r="H42" t="n">
-        <v>5589.5</v>
+        <v>5485.05</v>
       </c>
       <c r="I42" t="n">
         <v>5511.33051888476</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>56</v>
+        <v>56.16666666666666</v>
       </c>
       <c r="K42" t="n">
-        <v>12.86</v>
+        <v>10.75</v>
       </c>
       <c r="L42" t="n">
         <v>2.68</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>6.04</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45520.55208333334</v>
+        <v>45523.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>5555.1</v>
+        <v>5702.1</v>
       </c>
       <c r="I43" t="n">
         <v>5641.205811930383</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>14</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.28</v>
+        <v>-3.96</v>
       </c>
       <c r="L43" t="n">
-        <v>2.1</v>
+        <v>4.01</v>
       </c>
       <c r="M43" t="n">
         <v>1.88</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>6.25</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45559.55208333334</v>
+        <v>45560.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>6350</v>
+        <v>6095</v>
       </c>
       <c r="I44" t="n">
         <v>6204.354676046984</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K44" t="n">
-        <v>11.36</v>
+        <v>6.89</v>
       </c>
       <c r="L44" t="n">
         <v>2.35</v>
@@ -2949,7 +3476,7 @@
         <v>2.47</v>
       </c>
       <c r="N44" t="n">
-        <v>1.34</v>
+        <v>3.78</v>
       </c>
       <c r="O44" t="n">
         <v>2.16</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>7.85</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45574.38541666666</v>
+        <v>45574.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>6441</v>
+        <v>6451.05</v>
       </c>
       <c r="I45" t="n">
         <v>6445.895948024237</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K45" t="n">
-        <v>-5.68</v>
+        <v>-5.84</v>
       </c>
       <c r="L45" t="n">
-        <v>6.4</v>
+        <v>6.43</v>
       </c>
       <c r="M45" t="n">
         <v>1.49</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>4.76</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45582.55208333334</v>
+        <v>45583.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>6405</v>
+        <v>5999.95</v>
       </c>
       <c r="I46" t="n">
         <v>6209.606026459227</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.71</v>
+        <v>-6.99</v>
       </c>
       <c r="L46" t="n">
-        <v>2.14</v>
+        <v>7.11</v>
       </c>
       <c r="M46" t="n">
-        <v>0.12</v>
+        <v>0.39</v>
       </c>
       <c r="N46" t="n">
-        <v>1.6</v>
+        <v>6.21</v>
       </c>
       <c r="O46" t="n">
         <v>1.23</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>9.130000000000001</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45602.38541666666</v>
+        <v>45602.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>5969.1</v>
+        <v>5999</v>
       </c>
       <c r="I47" t="n">
         <v>5996.371482024</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K47" t="n">
-        <v>0.51</v>
+        <v>0.02</v>
       </c>
       <c r="L47" t="n">
         <v>6.33</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>5.85</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45644.55208333334</v>
+        <v>45645.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>6565</v>
+        <v>6276.25</v>
       </c>
       <c r="I48" t="n">
         <v>6486.271782651552</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>42</v>
+        <v>42.83333333333334</v>
       </c>
       <c r="K48" t="n">
-        <v>9.43</v>
+        <v>4.62</v>
       </c>
       <c r="L48" t="n">
         <v>4.79</v>
       </c>
       <c r="M48" t="n">
-        <v>0.65</v>
+        <v>2.97</v>
       </c>
       <c r="N48" t="n">
-        <v>2.54</v>
+        <v>5.22</v>
       </c>
       <c r="O48" t="n">
         <v>4.69</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>5.56</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45666.55208333334</v>
+        <v>45667.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>5821</v>
+        <v>6130</v>
       </c>
       <c r="I49" t="n">
         <v>5872.60566927366</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K49" t="n">
-        <v>7.25</v>
+        <v>2.33</v>
       </c>
       <c r="L49" t="n">
         <v>1.49</v>
@@ -3234,7 +3821,7 @@
         <v>1.91</v>
       </c>
       <c r="N49" t="n">
-        <v>1.91</v>
+        <v>4.95</v>
       </c>
       <c r="O49" t="n">
         <v>-5.22</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>7.53</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45670.55208333334</v>
+        <v>45671.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>6025</v>
+        <v>5735.1</v>
       </c>
       <c r="I50" t="n">
         <v>5797.314459069113</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K50" t="n">
-        <v>-1.71</v>
+        <v>-6.44</v>
       </c>
       <c r="L50" t="n">
-        <v>4.05</v>
+        <v>6.63</v>
       </c>
       <c r="M50" t="n">
         <v>0.25</v>
       </c>
       <c r="N50" t="n">
-        <v>1.38</v>
+        <v>4.27</v>
       </c>
       <c r="O50" t="n">
         <v>4.95</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>9.17</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45692.55208333334</v>
+        <v>45693.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>5903.6</v>
+        <v>6089.05</v>
       </c>
       <c r="I51" t="n">
         <v>6027.123838266626</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K51" t="n">
-        <v>-2.94</v>
+        <v>-6.17</v>
       </c>
       <c r="L51" t="n">
-        <v>5.66</v>
+        <v>6.28</v>
       </c>
       <c r="M51" t="n">
         <v>0.85</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,25 +4007,25 @@
         <v>7.53</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>5775.05</v>
+        <v>5668.3</v>
       </c>
       <c r="I52" t="n">
         <v>5717.260687821802</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K52" t="n">
-        <v>-5.16</v>
+        <v>-6.91</v>
       </c>
       <c r="L52" t="n">
-        <v>5.16</v>
+        <v>7.13</v>
       </c>
       <c r="M52" t="n">
-        <v>0.06</v>
+        <v>0.17</v>
       </c>
       <c r="N52" t="n">
         <v>2.78</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>7.18</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45762.38541666666</v>
+        <v>45762.55208333334</v>
       </c>
       <c r="H53" t="n">
-        <v>4289.4</v>
+        <v>4318</v>
       </c>
       <c r="I53" t="n">
         <v>4293.421761087389</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>63</v>
+        <v>63.16666666666666</v>
       </c>
       <c r="K53" t="n">
-        <v>24.33</v>
+        <v>23.82</v>
       </c>
       <c r="L53" t="n">
         <v>2.62</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>7.8</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45848.55208333334</v>
+        <v>45849.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>5307.5</v>
+        <v>5218.5</v>
       </c>
       <c r="I54" t="n">
         <v>5266.543046848666</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>86</v>
+        <v>86.83333333333333</v>
       </c>
       <c r="K54" t="n">
-        <v>22.92</v>
+        <v>20.85</v>
       </c>
       <c r="L54" t="n">
         <v>6.44</v>
@@ -3519,7 +4166,7 @@
         <v>3.04</v>
       </c>
       <c r="N54" t="n">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="O54" t="n">
         <v>2.08</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>121</v>
+        <v>122</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>4</v>
+      </c>
+      <c r="U54" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>4.16</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45889.55208333334</v>
+        <v>45890.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>5177</v>
+        <v>5225</v>
       </c>
       <c r="I55" t="n">
         <v>5223.363660010424</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K55" t="n">
-        <v>0.8</v>
+        <v>-0.12</v>
       </c>
       <c r="L55" t="n">
         <v>2.29</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>5.28</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45922.38541666666</v>
+        <v>45922.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>5302</v>
+        <v>5255</v>
       </c>
       <c r="I56" t="n">
         <v>5299.252710593079</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>32</v>
+        <v>32.16666666666666</v>
       </c>
       <c r="K56" t="n">
-        <v>1.47</v>
+        <v>0.57</v>
       </c>
       <c r="L56" t="n">
         <v>3.01</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>5.8</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45937.55208333334</v>
+        <v>45938.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>5272</v>
+        <v>5370</v>
       </c>
       <c r="I57" t="n">
         <v>5319.686673813928</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.32</v>
+        <v>-2.19</v>
       </c>
       <c r="L57" t="n">
         <v>4.68</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>6</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46017.38541666666</v>
+        <v>46017.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>6096</v>
+        <v>6020.5</v>
       </c>
       <c r="I58" t="n">
         <v>6078.164941894794</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>79</v>
+        <v>79.16666666666667</v>
       </c>
       <c r="K58" t="n">
-        <v>13.52</v>
+        <v>12.11</v>
       </c>
       <c r="L58" t="n">
         <v>1.94</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>108</v>
+        <v>109</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>4.53</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46036.55208333334</v>
+        <v>46038.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>6017</v>
+        <v>6341</v>
       </c>
       <c r="I59" t="n">
         <v>6215.900232847267</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>19</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K59" t="n">
-        <v>0.06</v>
+        <v>-5.32</v>
       </c>
       <c r="L59" t="n">
-        <v>2.16</v>
+        <v>5.81</v>
       </c>
       <c r="M59" t="n">
         <v>0.45</v>
       </c>
       <c r="N59" t="n">
-        <v>2.29</v>
+        <v>4.7</v>
       </c>
       <c r="O59" t="n">
         <v>-1.87</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>7.25</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46041.55208333334</v>
+        <v>46042.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>6360</v>
+        <v>5996</v>
       </c>
       <c r="I60" t="n">
         <v>6066.184535564598</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K60" t="n">
-        <v>0.3</v>
+        <v>-5.44</v>
       </c>
       <c r="L60" t="n">
-        <v>4.9</v>
+        <v>6.77</v>
       </c>
       <c r="M60" t="n">
-        <v>-0</v>
+        <v>1.8</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="O60" t="n">
         <v>4.7</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>8.25</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46118.55208333334</v>
+        <v>46119.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>4300</v>
+        <v>4405.1</v>
       </c>
       <c r="I61" t="n">
         <v>4356.140509154811</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>76.16666666666667</v>
+        <v>77</v>
       </c>
       <c r="K61" t="n">
-        <v>28.29</v>
+        <v>26.53</v>
       </c>
       <c r="L61" t="n">
         <v>4.66</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>4</v>
+      </c>
+      <c r="U61" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46135.55208333334</v>
+        <v>46136.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>4514.4</v>
+        <v>4253.8</v>
       </c>
       <c r="I62" t="n">
         <v>4496.594907590896</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K62" t="n">
-        <v>2.48</v>
+        <v>-3.43</v>
       </c>
       <c r="L62" t="n">
-        <v>3.19</v>
+        <v>3.75</v>
       </c>
       <c r="M62" t="n">
         <v>1.89</v>
       </c>
       <c r="N62" t="n">
-        <v>3.1</v>
+        <v>4.59</v>
       </c>
       <c r="O62" t="n">
         <v>3.6</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>10.31</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46160.55208333334</v>
+        <v>46161.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>4093.2</v>
+        <v>4255</v>
       </c>
       <c r="I63" t="n">
         <v>4216.792978271854</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K63" t="n">
-        <v>3.78</v>
+        <v>-0.03</v>
       </c>
       <c r="L63" t="n">
         <v>5.33</v>
@@ -4032,7 +4787,7 @@
         <v>1.13</v>
       </c>
       <c r="N63" t="n">
-        <v>3.29</v>
+        <v>3.95</v>
       </c>
       <c r="O63" t="n">
         <v>-4.59</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,25 +4835,25 @@
         <v>8.42</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46164.55208333334</v>
+        <v>46167.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>4008.2</v>
+        <v>3978.7</v>
       </c>
       <c r="I64" t="n">
         <v>3986.012746534228</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K64" t="n">
-        <v>-5.8</v>
+        <v>-6.49</v>
       </c>
       <c r="L64" t="n">
-        <v>5.99</v>
+        <v>8.32</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N64" t="n">
         <v>2.95</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>6.13</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46171.55208333334</v>
+        <v>46174.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>4025</v>
+        <v>4245.5</v>
       </c>
       <c r="I65" t="n">
         <v>4195.089524233196</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K65" t="n">
-        <v>-1.16</v>
+        <v>-6.71</v>
       </c>
       <c r="L65" t="n">
-        <v>4.29</v>
+        <v>7.41</v>
       </c>
       <c r="M65" t="n">
-        <v>0.82</v>
+        <v>1.41</v>
       </c>
       <c r="N65" t="n">
-        <v>0.95</v>
+        <v>4.6</v>
       </c>
       <c r="O65" t="n">
         <v>-0.15</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>8.69</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46177.55208333334</v>
+        <v>46178.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>4072.9</v>
+        <v>4020.8</v>
       </c>
       <c r="I66" t="n">
         <v>4046.515591601987</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K66" t="n">
-        <v>-4.07</v>
+        <v>-5.29</v>
       </c>
       <c r="L66" t="n">
         <v>5.95</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>9.119999999999999</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46205.55208333334</v>
+        <v>46206.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>3672.3</v>
+        <v>3771</v>
       </c>
       <c r="I67" t="n">
         <v>3756.258893409452</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K67" t="n">
-        <v>8.67</v>
+        <v>6.21</v>
       </c>
       <c r="L67" t="n">
         <v>2.66</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>6.75</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46252.55208333334</v>
+        <v>46253.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>4590</v>
+        <v>4561.4</v>
       </c>
       <c r="I68" t="n">
         <v>4577.602142442102</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>46.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K68" t="n">
-        <v>21.72</v>
+        <v>20.96</v>
       </c>
       <c r="L68" t="n">
         <v>1.74</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>6.19</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46307.55208333334</v>
+        <v>46308.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>4031</v>
+        <v>4166.9</v>
       </c>
       <c r="I69" t="n">
         <v>4155.740582004661</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>54.16666666666666</v>
+        <v>55</v>
       </c>
       <c r="K69" t="n">
-        <v>11.63</v>
+        <v>8.65</v>
       </c>
       <c r="L69" t="n">
         <v>3.04</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>3</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4410,22 +5249,22 @@
         <v>7.17</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46318.55208333334</v>
+        <v>46321.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>4118.5</v>
+        <v>4075.4</v>
       </c>
       <c r="I70" t="n">
         <v>4102.618672174</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K70" t="n">
-        <v>-1.16</v>
+        <v>-2.2</v>
       </c>
       <c r="L70" t="n">
-        <v>2.67</v>
+        <v>3.04</v>
       </c>
       <c r="M70" t="n">
         <v>4.26</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4491,6 +5342,12 @@
       <c r="Q71" t="n">
         <v>4</v>
       </c>
+      <c r="R71" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6593,7 +7450,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.3</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="6">
@@ -6603,7 +7460,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -6613,7 +7470,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>119</v>
+        <v>119.2</v>
       </c>
     </row>
     <row r="8">
@@ -6623,7 +7480,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -6633,7 +7490,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="10">
@@ -6643,7 +7500,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>54</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="11">
@@ -6653,7 +7510,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12">
@@ -6663,7 +7520,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -6673,7 +7530,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>72.5</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14">
@@ -6683,7 +7540,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.07</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="15">
@@ -6693,7 +7550,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.83</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="16">
@@ -6703,7 +7560,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.33</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="17">
@@ -6713,7 +7570,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31.87</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="18">
@@ -6723,7 +7580,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52.2</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="19">
@@ -6733,7 +7590,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.79</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="20">
@@ -6743,7 +7600,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.54</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="21">
@@ -6753,7 +7610,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11.25</v>
+        <v>12.87</v>
       </c>
     </row>
     <row r="22">
@@ -6763,7 +7620,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23">
@@ -6773,7 +7630,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -6783,7 +7640,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="25">
@@ -6793,7 +7650,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.53</v>
+        <v>9.24</v>
       </c>
     </row>
     <row r="26">
@@ -6803,7 +7660,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="27">
@@ -6813,7 +7670,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.94</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="28">
@@ -6823,7 +7680,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29">
